--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2018_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>31.13058172807248</v>
+      </c>
+      <c r="C2">
         <v>25.42193568542804</v>
-      </c>
-      <c r="C2">
-        <v>31.13058172807248</v>
       </c>
       <c r="D2">
         <v>3.933610769746397</v>
       </c>
       <c r="E2">
+        <v>19.88507258931365</v>
+      </c>
+      <c r="F2">
+        <v>63.87632830960555</v>
+      </c>
+      <c r="G2">
         <v>16.23859910108079</v>
-      </c>
-      <c r="F2">
-        <v>63.87632830960556</v>
-      </c>
-      <c r="G2">
-        <v>19.88507258931366</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>30.82489809004717</v>
+      </c>
+      <c r="C3">
         <v>24.4917588709097</v>
-      </c>
-      <c r="C3">
-        <v>30.82489809004717</v>
       </c>
       <c r="D3">
         <v>4.083006064491999</v>
       </c>
       <c r="E3">
-        <v>15.76891967039078</v>
+        <v>19.8464856849165</v>
       </c>
       <c r="F3">
-        <v>64.38459464469273</v>
+        <v>64.38459464469271</v>
       </c>
       <c r="G3">
-        <v>19.8464856849165</v>
+        <v>15.76891967039077</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.75749247480697</v>
+      </c>
+      <c r="C4">
         <v>30.59808925533307</v>
-      </c>
-      <c r="C4">
-        <v>32.75749247480697</v>
       </c>
       <c r="D4">
         <v>3.268177929854577</v>
       </c>
       <c r="E4">
+        <v>20.05287614164397</v>
+      </c>
+      <c r="F4">
+        <v>61.21615125781125</v>
+      </c>
+      <c r="G4">
         <v>18.73097260054478</v>
-      </c>
-      <c r="F4">
-        <v>61.21615125781124</v>
-      </c>
-      <c r="G4">
-        <v>20.05287614164397</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>46.29324546952224</v>
+      </c>
+      <c r="C5">
         <v>32.33113673805602</v>
-      </c>
-      <c r="C5">
-        <v>46.29324546952224</v>
       </c>
       <c r="D5">
         <v>3.092993630573249</v>
       </c>
       <c r="E5">
-        <v>18.10006917223888</v>
+        <v>25.91653216509108</v>
       </c>
       <c r="F5">
         <v>55.98339866267005</v>
       </c>
       <c r="G5">
-        <v>25.91653216509108</v>
+        <v>18.10006917223888</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.48270390352269</v>
+      </c>
+      <c r="C6">
         <v>30.33957473817835</v>
-      </c>
-      <c r="C6">
-        <v>29.48270390352269</v>
       </c>
       <c r="D6">
         <v>3.29602510460251</v>
       </c>
       <c r="E6">
-        <v>18.98332009531374</v>
+        <v>18.44718030182684</v>
       </c>
       <c r="F6">
         <v>62.56949960285941</v>
       </c>
       <c r="G6">
-        <v>18.44718030182684</v>
+        <v>18.98332009531374</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.55111472246204</v>
+      </c>
+      <c r="C7">
         <v>26.91584988065614</v>
-      </c>
-      <c r="C7">
-        <v>28.55111472246204</v>
       </c>
       <c r="D7">
         <v>3.715283018867924</v>
       </c>
       <c r="E7">
-        <v>17.31290628164506</v>
+        <v>18.36474700290726</v>
       </c>
       <c r="F7">
         <v>64.32234671544768</v>
       </c>
       <c r="G7">
-        <v>18.36474700290726</v>
+        <v>17.31290628164506</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>30.7425097698654</v>
+      </c>
+      <c r="C8">
         <v>31.20567375886525</v>
-      </c>
-      <c r="C8">
-        <v>30.7425097698654</v>
       </c>
       <c r="D8">
         <v>3.204545454545455</v>
       </c>
       <c r="E8">
-        <v>19.26892483689338</v>
+        <v>18.98292966306194</v>
       </c>
       <c r="F8">
         <v>61.74814550004469</v>
       </c>
       <c r="G8">
-        <v>18.98292966306194</v>
+        <v>19.26892483689338</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.51576805696846</v>
+      </c>
+      <c r="C9">
         <v>45.59511698880976</v>
-      </c>
-      <c r="C9">
-        <v>31.51576805696846</v>
       </c>
       <c r="D9">
         <v>2.193217313699241</v>
       </c>
       <c r="E9">
-        <v>25.74382538770822</v>
+        <v>17.79437105112005</v>
       </c>
       <c r="F9">
         <v>56.46180356117174</v>
       </c>
       <c r="G9">
-        <v>17.79437105112005</v>
+        <v>25.74382538770822</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>30.4110337293459</v>
+      </c>
+      <c r="C10">
         <v>29.40734671582685</v>
-      </c>
-      <c r="C10">
-        <v>30.4110337293459</v>
       </c>
       <c r="D10">
         <v>3.400510796377989</v>
       </c>
       <c r="E10">
-        <v>18.4004784893408</v>
+        <v>19.02849574913488</v>
       </c>
       <c r="F10">
         <v>62.57102576152433</v>
       </c>
       <c r="G10">
-        <v>19.02849574913488</v>
+        <v>18.4004784893408</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.5309244070051</v>
+      </c>
+      <c r="C11">
         <v>29.16759033473731</v>
-      </c>
-      <c r="C11">
-        <v>30.5309244070051</v>
       </c>
       <c r="D11">
         <v>3.428462853885617</v>
       </c>
       <c r="E11">
-        <v>18.2641588006663</v>
+        <v>19.11785119378123</v>
       </c>
       <c r="F11">
         <v>62.61799000555247</v>
       </c>
       <c r="G11">
-        <v>19.11785119378123</v>
+        <v>18.2641588006663</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>30.9374532497382</v>
+      </c>
+      <c r="C12">
         <v>27.04919147547226</v>
-      </c>
-      <c r="C12">
-        <v>30.9374532497382</v>
       </c>
       <c r="D12">
         <v>3.69696817336216</v>
       </c>
       <c r="E12">
-        <v>17.12118864383726</v>
+        <v>19.58232184976671</v>
       </c>
       <c r="F12">
         <v>63.29648950639601</v>
       </c>
       <c r="G12">
-        <v>19.58232184976671</v>
+        <v>17.12118864383726</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.81223675459987</v>
+      </c>
+      <c r="C13">
         <v>39.43693194413655</v>
-      </c>
-      <c r="C13">
-        <v>26.81223675459987</v>
       </c>
       <c r="D13">
         <v>2.535694210230467</v>
       </c>
       <c r="E13">
-        <v>23.72158143876258</v>
+        <v>16.12774184945663</v>
       </c>
       <c r="F13">
         <v>60.15067671178079</v>
       </c>
       <c r="G13">
-        <v>16.12774184945663</v>
+        <v>23.72158143876258</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.80891560230403</v>
+      </c>
+      <c r="C14">
         <v>28.68519909842224</v>
-      </c>
-      <c r="C14">
-        <v>30.80891560230403</v>
       </c>
       <c r="D14">
         <v>3.486118386589838</v>
       </c>
       <c r="E14">
-        <v>17.98511446785793</v>
+        <v>19.31664730081965</v>
       </c>
       <c r="F14">
         <v>62.69823823132243</v>
       </c>
       <c r="G14">
-        <v>19.31664730081965</v>
+        <v>17.98511446785793</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>30.11761761761762</v>
+      </c>
+      <c r="C15">
         <v>32.73273273273274</v>
-      </c>
-      <c r="C15">
-        <v>30.11761761761762</v>
       </c>
       <c r="D15">
         <v>3.055045871559633</v>
       </c>
       <c r="E15">
-        <v>20.09988474836727</v>
+        <v>18.49404533230888</v>
       </c>
       <c r="F15">
         <v>61.40606991932386</v>
       </c>
       <c r="G15">
-        <v>18.49404533230888</v>
+        <v>20.09988474836727</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>25.43918918918919</v>
+      </c>
+      <c r="C16">
         <v>42.02702702702702</v>
-      </c>
-      <c r="C16">
-        <v>25.43918918918919</v>
       </c>
       <c r="D16">
         <v>2.379421221864952</v>
       </c>
       <c r="E16">
-        <v>25.09582408714948</v>
+        <v>15.1906394996974</v>
       </c>
       <c r="F16">
         <v>59.71353641315311</v>
       </c>
       <c r="G16">
-        <v>15.1906394996974</v>
+        <v>25.09582408714948</v>
       </c>
     </row>
   </sheetData>
